--- a/exports/vixxo-sr-status-reference.xlsx
+++ b/exports/vixxo-sr-status-reference.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="SR Status" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="SR Sub-Status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP Invoice Status (Gateway)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +53,11 @@
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -74,6 +80,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -882,7 +888,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1859,7 +1864,6 @@
           <t>VixxoLink / Gateway</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Recently opened/transferred; not yet a health signal</t>
@@ -1887,7 +1891,6 @@
           <t>VixxoLink / Gateway</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Normal healthy path</t>
@@ -1915,7 +1918,6 @@
           <t>VixxoLink / Gateway</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Borderline; watch closely</t>
@@ -1943,7 +1945,6 @@
           <t>VixxoLink / Gateway</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Real problem path</t>
@@ -1971,7 +1972,6 @@
           <t>VixxoLink / Gateway</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Positive closed-out condition</t>
@@ -1999,7 +1999,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Invoice accepted in billing workflow</t>
@@ -2027,7 +2026,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Invoice billed</t>
@@ -2055,7 +2053,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Invoice paid</t>
@@ -2083,7 +2080,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>AR investigation hold</t>
@@ -2111,7 +2107,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>AP review required</t>
@@ -2139,7 +2134,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Visual audit review</t>
@@ -2167,7 +2161,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Paid-only pending state</t>
@@ -2195,7 +2188,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Invoice creation pending</t>
@@ -2223,7 +2215,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Rejected; do not process</t>
@@ -2251,7 +2242,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Payment disposition label in AP reply drafting</t>
@@ -2279,7 +2269,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Payment disposition label in AP reply drafting</t>
@@ -2307,7 +2296,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Payment disposition label in AP reply drafting</t>
@@ -2335,7 +2323,6 @@
           <t>Gateway</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Payment disposition label in AP reply drafting</t>
@@ -2354,4 +2341,565 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gateway SP invoice status reference — compiled 2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source: workspace-documented Gateway invoice.status values only. Gateway MCP bearer token was not available in this environment — re-run with GATEWAY_API_TOKEN or ~/.vixxo/gateway_api_token to refresh from live Gateway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Invoice Status</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Gateway Field</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Meaning / AP Notes</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Source Reference</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Sample SR</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Sample SP</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Data Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Creation Pending</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>AP review / hold</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Invoice creation pending in billing system</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Review</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>AP review / hold</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Invoice in AP line-item review (also appears as SR Substatus)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; sub-status-decoder.md</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PaidOnlyPending</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>AP review / hold</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Paid-only pending state</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ReviewByAP</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>AP review / hold</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Accounts payable review required</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>UnderARInvestigation</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>AP review / hold</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AR investigation hold</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>VisualAudit</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>AP review / hold</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Visual audit review</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Delinquent SC Invoice</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Delinquent / vendor billing</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SP missed Service Channel invoice SLA (also SR Substatus)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; sub-status-decoder.md</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Payment lifecycle</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Invoice accepted in billing workflow</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Billed</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Payment lifecycle</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Invoice billed to customer/AP</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Payment lifecycle</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Invoice paid</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>RejectedDoNotProcess</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Rejected; do not process payment</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>vixxo-freshdesk-invoice-review/SKILL.md; starbucks-completed-sr-report/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>AR Successful</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>SR billing overlap</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AR booked invoice successfully (SR Substatus)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>sub-status-decoder.md</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Required for SR</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>SR billing overlap</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Work complete; SP invoice not yet uploaded (SR Substatus in VixxoLink)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>sub-status-decoder.md; vixxo-spm-invoice-concerns/SKILL.md</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>No Invoice Pending</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>invoice.status</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SR billing overlap</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>No invoice expected on SR</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>sub-status-decoder.md</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/vixxo-sr-status-reference.xlsx
+++ b/exports/vixxo-sr-status-reference.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -81,6 +86,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +465,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vixxo SR Status reference — compiled 2026-07-02</t>
+          <t>Vixxo SR Status reference — compiled 2026-07-06</t>
         </is>
       </c>
     </row>
@@ -877,7 +883,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vixxo SR Sub-Status &amp; Invoice Status reference — compiled 2026-07-02</t>
+          <t>Vixxo SR Sub-Status &amp; Invoice Status reference — compiled 2026-07-06</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2365,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="59" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2369,10 +2375,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
+    <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: workspace-documented Gateway invoice.status values only. Gateway MCP bearer token was not available in this environment — re-run with GATEWAY_API_TOKEN or ~/.vixxo/gateway_api_token to refresh from live Gateway.</t>
+          <t>Source: workspace-documented Gateway invoice.status values only. Live Gateway MCP calls failed — picklist: no Gateway bearer token; sample: no Gateway bearer token. Authenticate Gateway MCP in Cursor (OAuth) or set GATEWAY_API_TOKEN / ~/.vixxo/gateway_api_token, then re-run this script.</t>
         </is>
       </c>
     </row>
@@ -2420,478 +2426,478 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Invoice Creation Pending</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>AP review / hold</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Invoice creation pending in billing system</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Invoice Review</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>AP review / hold</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Invoice in AP line-item review (also appears as SR Substatus)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; sub-status-decoder.md</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>PaidOnlyPending</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>AP review / hold</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Paid-only pending state</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ReviewByAP</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>AP review / hold</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Accounts payable review required</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>UnderARInvestigation</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>AP review / hold</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>AR investigation hold</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>VisualAudit</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>AP review / hold</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Visual audit review</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; vixxo-spm-invoice-concerns/SKILL.md</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Delinquent SC Invoice</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Delinquent / vendor billing</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>SP missed Service Channel invoice SLA (also SR Substatus)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; sub-status-decoder.md</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Payment lifecycle</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Invoice accepted in billing workflow</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Billed</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Payment lifecycle</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Invoice billed to customer/AP</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Payment lifecycle</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Invoice paid</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>RejectedDoNotProcess</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Rejection</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Rejected; do not process payment</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>vixxo-freshdesk-invoice-review/SKILL.md; starbucks-completed-sr-report/SKILL.md</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>AR Successful</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>SR billing overlap</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>AR booked invoice successfully (SR Substatus)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>sub-status-decoder.md</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Invoice Required for SR</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>SR billing overlap</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Work complete; SP invoice not yet uploaded (SR Substatus in VixxoLink)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>sub-status-decoder.md; vixxo-spm-invoice-concerns/SKILL.md</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>No Invoice Pending</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>invoice.status</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>SR billing overlap</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>No invoice expected on SR</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>sub-status-decoder.md</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Workspace documented (Gateway not queried or value not in sample)</t>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Workspace documented (not returned by live Gateway query)</t>
         </is>
       </c>
     </row>

--- a/exports/vixxo-sr-status-reference.xlsx
+++ b/exports/vixxo-sr-status-reference.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,6 +92,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2378,7 +2384,7 @@
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: workspace-documented Gateway invoice.status values only. Live Gateway MCP calls failed — picklist: no Gateway bearer token; sample: no Gateway bearer token. Authenticate Gateway MCP in Cursor (OAuth) or set GATEWAY_API_TOKEN / ~/.vixxo/gateway_api_token, then re-run this script.</t>
+          <t>Source: workspace-documented Gateway invoice.status values only. Live Gateway MCP calls failed — picklist: gateway_list_invoice_statuses: Gateway/Vixxo MCP OAuth not configured. Connect gateway in Cursor Settings → MCP (url OAuth, no API token), then retry.; sample: gateway_search_invoices returned no invoice rows. Authenticate Gateway MCP in Cursor (Settings → MCP → gateway; OAuth, no API token) or set GATEWAY_API_TOKEN / ~/.vixxo/gateway_api_token, then re-run this script.</t>
         </is>
       </c>
     </row>
